--- a/creches-parana/10_revisao_parecer/Material_Suplementar/Tabelas_1_a_7_dados_editaveis.xlsx
+++ b/creches-parana/10_revisao_parecer/Material_Suplementar/Tabelas_1_a_7_dados_editaveis.xlsx
@@ -1609,7 +1609,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mun/</t>
+          <t>Mun.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>100 após tetos</t>
+          <t>100 (cota fixa)</t>
         </is>
       </c>
     </row>
